--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98207</v>
+        <v>98210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98210</v>
+        <v>98211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543710</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98211</v>
+        <v>98216</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98216</v>
+        <v>98218</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543710</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52866-2025 artfynd.xlsx
+++ b/artfynd/A 52866-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136543710</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537564</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136538022</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136546177</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136550500</v>
       </c>
       <c r="B6" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136545527</v>
       </c>
       <c r="B7" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136542319</v>
       </c>
       <c r="B8" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>136548158</v>
       </c>
       <c r="B9" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
